--- a/space-battleship/config_excel/res.xlsx
+++ b/space-battleship/config_excel/res.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="172">
   <si>
     <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
   </si>
@@ -265,6 +265,33 @@
     <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
   </si>
   <si>
+    <t>hightech</t>
+  </si>
+  <si>
+    <t>这个高科技的名字</t>
+  </si>
+  <si>
+    <t>高科技的效果</t>
+  </si>
+  <si>
+    <t>timeCostBase</t>
+  </si>
+  <si>
+    <t>升级高科技需要的基础时间</t>
+  </si>
+  <si>
+    <t>timeCostMutiple</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>通过第几关后解锁</t>
+  </si>
+  <si>
+    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
+  </si>
+  <si>
     <t>如上</t>
   </si>
   <si>
@@ -488,6 +515,39 @@
   </si>
   <si>
     <t>死亡时后退距离</t>
+  </si>
+  <si>
+    <t>hightechLimit</t>
+  </si>
+  <si>
+    <t>同时研发的高科技数量</t>
+  </si>
+  <si>
+    <t>这个神器的名字</t>
+  </si>
+  <si>
+    <t>神器的效果</t>
+  </si>
+  <si>
+    <t>升级神器需要的基础时间</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>可变参数，具体效果参看神器的效果des</t>
+  </si>
+  <si>
+    <t>反物质炼铁炉</t>
+  </si>
+  <si>
+    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，点击获取，10秒后消失</t>
+  </si>
+  <si>
+    <t>正电子聚焦装置</t>
+  </si>
+  <si>
+    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）.</t>
   </si>
 </sst>
 </file>
@@ -1103,8 +1163,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1445,10 +1508,10 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1456,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1464,7 +1527,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/res.xlsx
+++ b/space-battleship/config_excel/res.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="0" firstSheet="0"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="res" sheetId="7" r:id="rId6" state="visible"/>
+    <sheet name="res" sheetId="7" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,213 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="172">
-  <si>
-    <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
-  </si>
-  <si>
-    <t>战舰会自动使用武器，攻击敌方飞行器，武器有各种参数，在武器表里定义</t>
-  </si>
-  <si>
-    <t>在每个关卡，敌方飞行器每隔一段距离就会出现。全部击落后才能前进，战斗时无法移动。关卡最后出现一个敌方BOSS飞行器，击毁后通关</t>
-  </si>
-  <si>
-    <t>敌方飞行器有各种参数，在怪物表里配置。怪物群负责整理一整群怪物，而关卡表将配置怪物群，用来辨别哪些敌方飞行器将出现在关卡里及出现在关卡的什么位置</t>
-  </si>
-  <si>
-    <t>敌方飞行器被击毁后会掉落资源，鼠标划过可以拾取。如果一段时间没有拾取，则自动拾取，但会有损耗，损耗比例在config里配置</t>
-  </si>
-  <si>
-    <t>飞行器初始武器为激光，激光会发射一道光束，攻击一个目标。</t>
-  </si>
-  <si>
-    <t>第二个武器为导弹，导弹在通关第一关后获得，导弹会同时发射3枚导弹，锁定3个敌人（若不足则只发射对应数量的导弹）</t>
-  </si>
-  <si>
-    <t>玩家可以选择任何一个已经通关过的关卡重新通关，或者无限循环该关卡。如果选择循环，则击败BOSS后就从这关开始重新前进</t>
-  </si>
-  <si>
-    <t>具体配置如下，表格均从第四行开始是实际配置</t>
-  </si>
-  <si>
-    <t>表格名</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>列名</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>关卡的id</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>关卡长度</t>
-  </si>
-  <si>
-    <t>monGroup</t>
-  </si>
-  <si>
-    <t>怪物群id</t>
-  </si>
-  <si>
-    <t>格式为{id|比例，id|比例....}，id为monGroup表的id，比例表示在关卡长度的%多少处出现</t>
-  </si>
-  <si>
-    <t>atkRatio</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的器伤害*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>所有倍率，在关卡中由上一关的倍率线性成长到本关倍率。如第一关倍率是1，第二关倍率是10，则10%的长度时是2..以此类推</t>
-  </si>
-  <si>
-    <t>lifeRatio</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的生命*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>resRatio</t>
-  </si>
-  <si>
-    <t>资源倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器摧毁时获得的资源乘该值</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
-  <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>武器名</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>武器说明</t>
-  </si>
-  <si>
-    <t>武器等级</t>
-  </si>
-  <si>
-    <t>dmg</t>
-  </si>
-  <si>
-    <t>武器命中时的伤害</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>武器发射需要的时间</t>
-  </si>
-  <si>
-    <t>unlock</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器</t>
-  </si>
-  <si>
-    <t>res_1</t>
-  </si>
-  <si>
-    <t>升级该武器需要的资源</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为res_x。如res_2，res_3就表示第二种，第三种资源。资源为res表的id</t>
-  </si>
-  <si>
-    <t>cost_1</t>
-  </si>
-  <si>
-    <t>升到该等级需要的资源数量</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为cost_x。如cost_2，cost_3就表示第二种，第三种资源消耗量。与res_x一一对应</t>
-  </si>
-  <si>
-    <t>para1</t>
-  </si>
-  <si>
-    <t>武器的额外参数。具体每个武器再定义，一般可参考des</t>
-  </si>
-  <si>
-    <t>mon</t>
-  </si>
-  <si>
-    <t>敌方飞行器id</t>
-  </si>
-  <si>
-    <t>飞行器描述</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的</t>
-  </si>
-  <si>
-    <t>dmgMultiple</t>
-  </si>
-  <si>
-    <t>武器的伤害乘该值，这样计算完后的就是这个飞行器的伤害</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>飞行器生命</t>
-  </si>
-  <si>
-    <t>res</t>
-  </si>
-  <si>
-    <t>掉落的资源</t>
-  </si>
-  <si>
-    <t>格式为｛id，数量，概率｝，id为res表的id，数量就是掉出来的数量，概率是被击毁时有多大概率掉落该资源</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>大小</t>
-  </si>
-  <si>
-    <t>战场中占据的格子数</t>
-  </si>
-  <si>
-    <t>敌方飞行器组id</t>
-  </si>
-  <si>
-    <t>飞行器组描述</t>
-  </si>
-  <si>
-    <t>格式为{id1，id2....｝</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置</t>
   </si>
   <si>
     <t>资源id</t>
@@ -247,307 +46,13 @@
     <t>资源名</t>
   </si>
   <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>这个配置的名字</t>
-  </si>
-  <si>
-    <t>配置的描述</t>
-  </si>
-  <si>
-    <t>para_1</t>
-  </si>
-  <si>
-    <t>配置的参数</t>
-  </si>
-  <si>
-    <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
-  </si>
-  <si>
-    <t>hightech</t>
-  </si>
-  <si>
-    <t>这个高科技的名字</t>
-  </si>
-  <si>
-    <t>高科技的效果</t>
-  </si>
-  <si>
-    <t>timeCostBase</t>
-  </si>
-  <si>
-    <t>升级高科技需要的基础时间</t>
-  </si>
-  <si>
-    <t>timeCostMutiple</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>通过第几关后解锁</t>
-  </si>
-  <si>
-    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
-  </si>
-  <si>
     <t>如上</t>
-  </si>
-  <si>
-    <t>{2|0.1，2|0.2，2|0.3，2|0.4，2|0.5，2|0.6，2|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，8|0.9}</t>
-  </si>
-  <si>
-    <t>dmgtype</t>
-  </si>
-  <si>
-    <t>res_2</t>
-  </si>
-  <si>
-    <t>cost_2</t>
-  </si>
-  <si>
-    <t>para2</t>
-  </si>
-  <si>
-    <t>para3</t>
-  </si>
-  <si>
-    <t>伤害类型，1为能量，2为物理。</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器。不填则这行无意义</t>
-  </si>
-  <si>
-    <t>armour</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础生命，如果没了，飞船就会爆炸！然后后退。额外参数para1是生命值，dmgtype表明护甲对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础护盾，护盾会先于护甲被扣除，同时护盾会缓慢恢复。额外参数para1是护盾值，para2是每秒恢复的比例，para3是连续多少秒不受攻击后才开始恢复，被攻击会立即停止恢复，dmgtype表明护盾对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>laser</t>
-  </si>
-  <si>
-    <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>missile</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发。para2是导弹飞行速度</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发</t>
-  </si>
-  <si>
-    <t>cannon</t>
-  </si>
-  <si>
-    <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>laser_mon</t>
-  </si>
-  <si>
-    <t>missile-mon</t>
-  </si>
-  <si>
-    <t>cannon-mon</t>
-  </si>
-  <si>
-    <t>armourType</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的,格式为｛name|数量，name|数量...}</t>
-  </si>
-  <si>
-    <t>护甲类型</t>
-  </si>
-  <si>
-    <t>1为能量，2为物理</t>
-  </si>
-  <si>
-    <t>激光飞船</t>
-  </si>
-  <si>
-    <t>｛laser_mon|1｝</t>
-  </si>
-  <si>
-    <t>{1,10,0.5}</t>
-  </si>
-  <si>
-    <t>火炮飞船</t>
-  </si>
-  <si>
-    <t>｛cannon-mon|1｝</t>
-  </si>
-  <si>
-    <t>激光飞船-弱</t>
-  </si>
-  <si>
-    <t>{1,5,0.2}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛laser_mon|2,cannon-mon|2｝</t>
-  </si>
-  <si>
-    <t>{2,1,1}</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗能量</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置，null表示此处无飞船｝</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，1，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，2，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>基础飞船组</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>激光飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，3，3，3，3，3，3，null，null}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，4，4，4，4，4，4，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，5，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗能量</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，6，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-双BOSS</t>
-  </si>
-  <si>
-    <t>｛null，null，null，5，null，null，6，null，null，null}</t>
   </si>
   <si>
     <t>铁</t>
   </si>
   <si>
-    <t>铝</t>
-  </si>
-  <si>
-    <t>startEquip</t>
-  </si>
-  <si>
-    <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
-  </si>
-  <si>
-    <t>armour,laser</t>
-  </si>
-  <si>
-    <t>dmgReduce</t>
-  </si>
-  <si>
-    <t>护甲类型对应时，减少的伤害</t>
-  </si>
-  <si>
-    <t>movement</t>
-  </si>
-  <si>
-    <t>飞船的移动速度，单位是秒</t>
-  </si>
-  <si>
-    <t>autoCollectReduce</t>
-  </si>
-  <si>
-    <t>自动拾取时的损耗</t>
-  </si>
-  <si>
-    <t>backRange</t>
-  </si>
-  <si>
-    <t>死亡时后退距离</t>
-  </si>
-  <si>
-    <t>hightechLimit</t>
-  </si>
-  <si>
-    <t>同时研发的高科技数量</t>
-  </si>
-  <si>
-    <t>这个神器的名字</t>
-  </si>
-  <si>
-    <t>神器的效果</t>
-  </si>
-  <si>
-    <t>升级神器需要的基础时间</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>可变参数，具体效果参看神器的效果des</t>
-  </si>
-  <si>
-    <t>反物质炼铁炉</t>
-  </si>
-  <si>
-    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，点击获取，10秒后消失</t>
-  </si>
-  <si>
-    <t>正电子聚焦装置</t>
-  </si>
-  <si>
-    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）.</t>
+    <t>铀</t>
   </si>
 </sst>
 </file>
@@ -1163,18 +668,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1484,7 +980,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
@@ -1492,26 +988,26 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1519,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1527,7 +1023,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
